--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/138.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/138.xlsx
@@ -426,13 +426,13 @@
         <v>-8.852805833128791</v>
       </c>
       <c r="E2">
-        <v>-14.15791831224237</v>
+        <v>-18.98574709418978</v>
       </c>
       <c r="F2">
-        <v>-5.125670901467147</v>
+        <v>-5.756594448707182</v>
       </c>
       <c r="G2">
-        <v>-13.13525707254518</v>
+        <v>-13.29750035377349</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.695460954064492</v>
       </c>
       <c r="E3">
-        <v>-14.68994155255951</v>
+        <v>-19.49987380522861</v>
       </c>
       <c r="F3">
-        <v>-5.377480509672349</v>
+        <v>-5.845492353273417</v>
       </c>
       <c r="G3">
-        <v>-12.91064761313651</v>
+        <v>-13.63758584352369</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.581433021170858</v>
       </c>
       <c r="E4">
-        <v>-14.89832834097048</v>
+        <v>-19.94166267246891</v>
       </c>
       <c r="F4">
-        <v>-5.02592469739385</v>
+        <v>-5.9885538888391</v>
       </c>
       <c r="G4">
-        <v>-13.00190166592623</v>
+        <v>-15.19078324029167</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.521876365096796</v>
       </c>
       <c r="E5">
-        <v>-15.14628493526047</v>
+        <v>-19.95198306473239</v>
       </c>
       <c r="F5">
-        <v>-4.952065803025441</v>
+        <v>-5.793128764640252</v>
       </c>
       <c r="G5">
-        <v>-12.65918463648535</v>
+        <v>-13.95620394122123</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.500956256116472</v>
       </c>
       <c r="E6">
-        <v>-16.46104585085542</v>
+        <v>-21.4353345391589</v>
       </c>
       <c r="F6">
-        <v>-5.132017024139994</v>
+        <v>-5.909617930658932</v>
       </c>
       <c r="G6">
-        <v>-12.94566480961891</v>
+        <v>-13.50736400349401</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.501522111405771</v>
       </c>
       <c r="E7">
-        <v>-16.33924801394512</v>
+        <v>-21.54869130051891</v>
       </c>
       <c r="F7">
-        <v>-5.059248261273669</v>
+        <v>-6.145045745106371</v>
       </c>
       <c r="G7">
-        <v>-12.97522533464795</v>
+        <v>-13.7102320888498</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.506658855507636</v>
       </c>
       <c r="E8">
-        <v>-17.65818418257514</v>
+        <v>-22.70738741638751</v>
       </c>
       <c r="F8">
-        <v>-4.86478735673168</v>
+        <v>-6.092663104022941</v>
       </c>
       <c r="G8">
-        <v>-12.28990939974232</v>
+        <v>-14.92791309688909</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.494015626723376</v>
       </c>
       <c r="E9">
-        <v>-17.82070205776241</v>
+        <v>-22.24769749139489</v>
       </c>
       <c r="F9">
-        <v>-4.877721485358991</v>
+        <v>-6.11667498992789</v>
       </c>
       <c r="G9">
-        <v>-12.20262890626109</v>
+        <v>-13.65385742123698</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.446908576907511</v>
       </c>
       <c r="E10">
-        <v>-18.58404427886537</v>
+        <v>-23.92473632760347</v>
       </c>
       <c r="F10">
-        <v>-4.709070023986025</v>
+        <v>-5.665925494633762</v>
       </c>
       <c r="G10">
-        <v>-12.39019993670675</v>
+        <v>-13.91256697570218</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.34981705004229</v>
       </c>
       <c r="E11">
-        <v>-18.92526026686932</v>
+        <v>-23.33905972724344</v>
       </c>
       <c r="F11">
-        <v>-4.829003541665546</v>
+        <v>-5.91225959430646</v>
       </c>
       <c r="G11">
-        <v>-11.88044904256078</v>
+        <v>-13.65709926813771</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.200237703852801</v>
       </c>
       <c r="E12">
-        <v>-20.51283457058237</v>
+        <v>-24.7244920082021</v>
       </c>
       <c r="F12">
-        <v>-4.709412968090784</v>
+        <v>-5.943938848891722</v>
       </c>
       <c r="G12">
-        <v>-11.90379165273467</v>
+        <v>-13.47995924102953</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.00501383169401</v>
       </c>
       <c r="E13">
-        <v>-20.15865356149445</v>
+        <v>-23.5407670164931</v>
       </c>
       <c r="F13">
-        <v>-4.484820199271963</v>
+        <v>-5.079501844272117</v>
       </c>
       <c r="G13">
-        <v>-11.78273098329895</v>
+        <v>-12.65026955750834</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.785697075871094</v>
       </c>
       <c r="E14">
-        <v>-21.52964001036864</v>
+        <v>-25.80258128673417</v>
       </c>
       <c r="F14">
-        <v>-4.358295362168366</v>
+        <v>-4.405306869012044</v>
       </c>
       <c r="G14">
-        <v>-10.47141047439623</v>
+        <v>-12.62699257176564</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.572865925786211</v>
       </c>
       <c r="E15">
-        <v>-22.27208332392619</v>
+        <v>-26.606589204426</v>
       </c>
       <c r="F15">
-        <v>-3.986274733203706</v>
+        <v>-4.595056019766909</v>
       </c>
       <c r="G15">
-        <v>-10.35096667461369</v>
+        <v>-13.21906931483808</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.396265657834987</v>
       </c>
       <c r="E16">
-        <v>-23.05598028854996</v>
+        <v>-27.17911964474176</v>
       </c>
       <c r="F16">
-        <v>-3.975077691020064</v>
+        <v>-4.583351188365353</v>
       </c>
       <c r="G16">
-        <v>-10.44453398860282</v>
+        <v>-12.12802705288556</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.282296150979067</v>
       </c>
       <c r="E17">
-        <v>-24.80256742856834</v>
+        <v>-28.53308355982111</v>
       </c>
       <c r="F17">
-        <v>-3.569062520579318</v>
+        <v>-4.630878768100974</v>
       </c>
       <c r="G17">
-        <v>-9.791935113866417</v>
+        <v>-12.1781214624336</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.242495380923154</v>
       </c>
       <c r="E18">
-        <v>-25.00019456273708</v>
+        <v>-28.74120316826563</v>
       </c>
       <c r="F18">
-        <v>-3.309550752262886</v>
+        <v>-4.778206395791075</v>
       </c>
       <c r="G18">
-        <v>-9.586750486089661</v>
+        <v>-11.64918526582955</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.281123309812169</v>
       </c>
       <c r="E19">
-        <v>-25.73685954346085</v>
+        <v>-29.98202995297435</v>
       </c>
       <c r="F19">
-        <v>-3.004675099866945</v>
+        <v>-4.377670047352444</v>
       </c>
       <c r="G19">
-        <v>-9.982403462949064</v>
+        <v>-12.20141813550566</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.385378941617251</v>
       </c>
       <c r="E20">
-        <v>-26.12633095049054</v>
+        <v>-29.72432808261985</v>
       </c>
       <c r="F20">
-        <v>-2.608072668224208</v>
+        <v>-4.236305008227694</v>
       </c>
       <c r="G20">
-        <v>-10.30797939096341</v>
+        <v>-12.0162423967984</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.53976345816812</v>
       </c>
       <c r="E21">
-        <v>-26.25137117479034</v>
+        <v>-30.40832464639741</v>
       </c>
       <c r="F21">
-        <v>-2.313067841800026</v>
+        <v>-3.362041909476082</v>
       </c>
       <c r="G21">
-        <v>-9.615090396698585</v>
+        <v>-12.19331679947539</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.715544775053131</v>
       </c>
       <c r="E22">
-        <v>-26.78015202771799</v>
+        <v>-30.67240487239171</v>
       </c>
       <c r="F22">
-        <v>-2.046784169965708</v>
+        <v>-3.092699905190628</v>
       </c>
       <c r="G22">
-        <v>-9.63260883860446</v>
+        <v>-11.89916513033585</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.886503706300005</v>
       </c>
       <c r="E23">
-        <v>-27.95041386620218</v>
+        <v>-32.8300212199533</v>
       </c>
       <c r="F23">
-        <v>-1.954582736197109</v>
+        <v>-3.196286420543304</v>
       </c>
       <c r="G23">
-        <v>-9.609344977747996</v>
+        <v>-11.56645254542971</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.020184527744735</v>
       </c>
       <c r="E24">
-        <v>-27.57470902015581</v>
+        <v>-32.64933510704724</v>
       </c>
       <c r="F24">
-        <v>-2.163424927219101</v>
+        <v>-2.716779322493588</v>
       </c>
       <c r="G24">
-        <v>-10.63490061981712</v>
+        <v>-12.08455414844448</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.095619280118003</v>
       </c>
       <c r="E25">
-        <v>-27.62062774659359</v>
+        <v>-32.90456669483056</v>
       </c>
       <c r="F25">
-        <v>-1.928361594428894</v>
+        <v>-3.121863407973588</v>
       </c>
       <c r="G25">
-        <v>-10.30497379201496</v>
+        <v>-12.78233216283287</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.092045366956439</v>
       </c>
       <c r="E26">
-        <v>-29.25114104084736</v>
+        <v>-33.72516014857548</v>
       </c>
       <c r="F26">
-        <v>-1.82180786703939</v>
+        <v>-2.809940834082031</v>
       </c>
       <c r="G26">
-        <v>-10.22356012268201</v>
+        <v>-11.66929587276739</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.003253966440127</v>
       </c>
       <c r="E27">
-        <v>-28.69953215044704</v>
+        <v>-33.62184301409049</v>
       </c>
       <c r="F27">
-        <v>-1.973767725245946</v>
+        <v>-2.685070246681825</v>
       </c>
       <c r="G27">
-        <v>-10.83545216275194</v>
+        <v>-12.79841342969571</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.826247215374822</v>
       </c>
       <c r="E28">
-        <v>-28.69042086074361</v>
+        <v>-33.56188375399193</v>
       </c>
       <c r="F28">
-        <v>-2.065042215890812</v>
+        <v>-2.962133463528773</v>
       </c>
       <c r="G28">
-        <v>-10.33861615666394</v>
+        <v>-13.22687862214956</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.573302536171085</v>
       </c>
       <c r="E29">
-        <v>-28.59706184060148</v>
+        <v>-33.51891532837015</v>
       </c>
       <c r="F29">
-        <v>-2.418742671375159</v>
+        <v>-2.696121496202573</v>
       </c>
       <c r="G29">
-        <v>-10.64958408629564</v>
+        <v>-12.82609381477118</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.25835356421591</v>
       </c>
       <c r="E30">
-        <v>-27.84547100954843</v>
+        <v>-30.7246476127812</v>
       </c>
       <c r="F30">
-        <v>-2.185005554796834</v>
+        <v>-2.722308674907274</v>
       </c>
       <c r="G30">
-        <v>-10.0872319293302</v>
+        <v>-12.76053828923504</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.906131792652014</v>
       </c>
       <c r="E31">
-        <v>-27.08742257456044</v>
+        <v>-32.94363836856873</v>
       </c>
       <c r="F31">
-        <v>-2.215472079504397</v>
+        <v>-3.277343827642041</v>
       </c>
       <c r="G31">
-        <v>-10.56752729753704</v>
+        <v>-13.01732996969874</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.538540950248891</v>
       </c>
       <c r="E32">
-        <v>-27.62401051667732</v>
+        <v>-33.08268742721126</v>
       </c>
       <c r="F32">
-        <v>-2.330340130515799</v>
+        <v>-3.433598770832112</v>
       </c>
       <c r="G32">
-        <v>-10.40698697029809</v>
+        <v>-12.19179103145025</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.181614318557159</v>
       </c>
       <c r="E33">
-        <v>-27.93234978338559</v>
+        <v>-33.78057508500735</v>
       </c>
       <c r="F33">
-        <v>-2.43501429226835</v>
+        <v>-3.199058137873071</v>
       </c>
       <c r="G33">
-        <v>-9.838512053902734</v>
+        <v>-11.92382351035508</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.8561557534992</v>
       </c>
       <c r="E34">
-        <v>-27.73306069925603</v>
+        <v>-33.36639632379181</v>
       </c>
       <c r="F34">
-        <v>-2.302507814149138</v>
+        <v>-3.097347046320333</v>
       </c>
       <c r="G34">
-        <v>-10.01323710194317</v>
+        <v>-12.60571056873108</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.581490098175926</v>
       </c>
       <c r="E35">
-        <v>-27.73204632107831</v>
+        <v>-32.72640067770978</v>
       </c>
       <c r="F35">
-        <v>-2.397001340521283</v>
+        <v>-3.381751255090891</v>
       </c>
       <c r="G35">
-        <v>-10.0001679964719</v>
+        <v>-12.43674078330591</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.371172264151686</v>
       </c>
       <c r="E36">
-        <v>-27.60483695772884</v>
+        <v>-31.53390856032193</v>
       </c>
       <c r="F36">
-        <v>-2.30087510199822</v>
+        <v>-3.593610360193878</v>
       </c>
       <c r="G36">
-        <v>-10.23294441634203</v>
+        <v>-11.93033017270746</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.232675256515487</v>
       </c>
       <c r="E37">
-        <v>-26.799053878226</v>
+        <v>-31.98033005647208</v>
       </c>
       <c r="F37">
-        <v>-2.583126383888901</v>
+        <v>-3.309112545906805</v>
       </c>
       <c r="G37">
-        <v>-9.561596641614958</v>
+        <v>-12.24021529922453</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.170568850097438</v>
       </c>
       <c r="E38">
-        <v>-25.80369529134006</v>
+        <v>-30.6362676498105</v>
       </c>
       <c r="F38">
-        <v>-2.73877413377272</v>
+        <v>-3.561168179230638</v>
       </c>
       <c r="G38">
-        <v>-9.524741961059275</v>
+        <v>-11.6107096618235</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.181605510626975</v>
       </c>
       <c r="E39">
-        <v>-26.22168249919605</v>
+        <v>-30.77009311368517</v>
       </c>
       <c r="F39">
-        <v>-2.652340622229814</v>
+        <v>-3.717661692232715</v>
       </c>
       <c r="G39">
-        <v>-9.16916254310537</v>
+        <v>-11.26574171439284</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.261667394983745</v>
       </c>
       <c r="E40">
-        <v>-25.79391378748349</v>
+        <v>-29.95008156885023</v>
       </c>
       <c r="F40">
-        <v>-2.554080509277139</v>
+        <v>-3.214753215053913</v>
       </c>
       <c r="G40">
-        <v>-9.173126258749178</v>
+        <v>-11.89901747536567</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.396601563650225</v>
       </c>
       <c r="E41">
-        <v>-25.46234344911587</v>
+        <v>-30.36904692709188</v>
       </c>
       <c r="F41">
-        <v>-2.617317248439451</v>
+        <v>-3.86623932633364</v>
       </c>
       <c r="G41">
-        <v>-9.006532077733052</v>
+        <v>-11.79474353542808</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.57556934313038</v>
       </c>
       <c r="E42">
-        <v>-24.94922658778075</v>
+        <v>-29.95271034801168</v>
       </c>
       <c r="F42">
-        <v>-3.048552892825831</v>
+        <v>-3.589473493384297</v>
       </c>
       <c r="G42">
-        <v>-9.008684559076048</v>
+        <v>-11.22120897538806</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.780485750199162</v>
       </c>
       <c r="E43">
-        <v>-24.49115332800887</v>
+        <v>-30.33189985480696</v>
       </c>
       <c r="F43">
-        <v>-2.969489366065633</v>
+        <v>-4.08912151646568</v>
       </c>
       <c r="G43">
-        <v>-8.682806758678236</v>
+        <v>-11.72862692100527</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.999609984696637</v>
       </c>
       <c r="E44">
-        <v>-24.77172852057611</v>
+        <v>-27.34065936954338</v>
       </c>
       <c r="F44">
-        <v>-3.152049944499005</v>
+        <v>-4.179283509688587</v>
       </c>
       <c r="G44">
-        <v>-9.090009635426885</v>
+        <v>-11.01976494018907</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.216690417894197</v>
       </c>
       <c r="E45">
-        <v>-23.37854802059033</v>
+        <v>-30.09227565269108</v>
       </c>
       <c r="F45">
-        <v>-3.204909725206447</v>
+        <v>-3.841945795511739</v>
       </c>
       <c r="G45">
-        <v>-8.715074291493815</v>
+        <v>-10.48283896908777</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.423145663545063</v>
       </c>
       <c r="E46">
-        <v>-23.69083158815928</v>
+        <v>-28.77248133823661</v>
       </c>
       <c r="F46">
-        <v>-3.448849843085053</v>
+        <v>-4.495216210177096</v>
       </c>
       <c r="G46">
-        <v>-8.856488378262764</v>
+        <v>-11.19491654703223</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.609430414853882</v>
       </c>
       <c r="E47">
-        <v>-23.40227269591651</v>
+        <v>-29.22599895315678</v>
       </c>
       <c r="F47">
-        <v>-3.233433728354445</v>
+        <v>-4.250037683031304</v>
       </c>
       <c r="G47">
-        <v>-8.518607869400503</v>
+        <v>-11.58023367597938</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.774358466679506</v>
       </c>
       <c r="E48">
-        <v>-22.78847880044287</v>
+        <v>-27.08383149467236</v>
       </c>
       <c r="F48">
-        <v>-3.25162716162213</v>
+        <v>-3.725537809498533</v>
       </c>
       <c r="G48">
-        <v>-8.816345913704517</v>
+        <v>-11.36248196962995</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.919202829085105</v>
       </c>
       <c r="E49">
-        <v>-22.75870408384243</v>
+        <v>-28.50171934884399</v>
       </c>
       <c r="F49">
-        <v>-3.350472101961181</v>
+        <v>-4.248057884938613</v>
       </c>
       <c r="G49">
-        <v>-9.556819183024405</v>
+        <v>-11.44750826389984</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.049881918090882</v>
       </c>
       <c r="E50">
-        <v>-22.16164289982713</v>
+        <v>-26.3181842802995</v>
       </c>
       <c r="F50">
-        <v>-3.290004595026429</v>
+        <v>-4.290639282912119</v>
       </c>
       <c r="G50">
-        <v>-8.676834935440047</v>
+        <v>-11.26264752246229</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.174467494307801</v>
       </c>
       <c r="E51">
-        <v>-21.15143997514404</v>
+        <v>-27.74364827148596</v>
       </c>
       <c r="F51">
-        <v>-3.509720764944969</v>
+        <v>-4.411429332486135</v>
       </c>
       <c r="G51">
-        <v>-8.971199883980951</v>
+        <v>-10.79553938370286</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.30023574416824</v>
       </c>
       <c r="E52">
-        <v>-21.86923027620384</v>
+        <v>-26.98377033299888</v>
       </c>
       <c r="F52">
-        <v>-3.66820981502039</v>
+        <v>-3.842639967395285</v>
       </c>
       <c r="G52">
-        <v>-8.610373792753494</v>
+        <v>-10.70099754691058</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.436967132079881</v>
       </c>
       <c r="E53">
-        <v>-20.7854351204221</v>
+        <v>-25.47069395518602</v>
       </c>
       <c r="F53">
-        <v>-3.417605481386262</v>
+        <v>-4.02686142247127</v>
       </c>
       <c r="G53">
-        <v>-8.835583715707541</v>
+        <v>-12.16003208797638</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.587332446646458</v>
       </c>
       <c r="E54">
-        <v>-21.0512293738283</v>
+        <v>-25.41060563357824</v>
       </c>
       <c r="F54">
-        <v>-3.423731258329964</v>
+        <v>-4.645702402774072</v>
       </c>
       <c r="G54">
-        <v>-8.852944658978563</v>
+        <v>-10.59558830431341</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.757687600603179</v>
       </c>
       <c r="E55">
-        <v>-20.51718643410373</v>
+        <v>-24.63296249155906</v>
       </c>
       <c r="F55">
-        <v>-3.594529019643583</v>
+        <v>-4.466196014954821</v>
       </c>
       <c r="G55">
-        <v>-8.669527655027164</v>
+        <v>-11.30078516064771</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.944626698419992</v>
       </c>
       <c r="E56">
-        <v>-20.39016273818858</v>
+        <v>-25.38050033837525</v>
       </c>
       <c r="F56">
-        <v>-3.621232271240228</v>
+        <v>-4.368310324068212</v>
       </c>
       <c r="G56">
-        <v>-9.002532268652089</v>
+        <v>-11.08551733901878</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.150260811209915</v>
       </c>
       <c r="E57">
-        <v>-19.93120189751119</v>
+        <v>-24.31317524255941</v>
       </c>
       <c r="F57">
-        <v>-3.598534176036118</v>
+        <v>-4.367836497913811</v>
       </c>
       <c r="G57">
-        <v>-9.584155039836141</v>
+        <v>-10.87454463641117</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.367139937067119</v>
       </c>
       <c r="E58">
-        <v>-19.46641291078593</v>
+        <v>-23.95173056116319</v>
       </c>
       <c r="F58">
-        <v>-3.362072559069986</v>
+        <v>-4.044093121184305</v>
       </c>
       <c r="G58">
-        <v>-9.602132852760338</v>
+        <v>-11.72215307086848</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.594286484967906</v>
       </c>
       <c r="E59">
-        <v>-18.3003263253368</v>
+        <v>-23.62004248247137</v>
       </c>
       <c r="F59">
-        <v>-3.682219992903939</v>
+        <v>-4.577167425703454</v>
       </c>
       <c r="G59">
-        <v>-9.412990117187707</v>
+        <v>-12.51160841562776</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.82073299489627</v>
       </c>
       <c r="E60">
-        <v>-19.26154474667892</v>
+        <v>-22.56682358318943</v>
       </c>
       <c r="F60">
-        <v>-3.452908014991368</v>
+        <v>-4.297778981556848</v>
       </c>
       <c r="G60">
-        <v>-8.997485749893663</v>
+        <v>-12.52718109314889</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.043461291222442</v>
       </c>
       <c r="E61">
-        <v>-18.37820702132072</v>
+        <v>-22.04186023385024</v>
       </c>
       <c r="F61">
-        <v>-3.910700289944098</v>
+        <v>-4.834122023847444</v>
       </c>
       <c r="G61">
-        <v>-8.895735069335283</v>
+        <v>-11.93427748224347</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.250482140297088</v>
       </c>
       <c r="E62">
-        <v>-17.97809370037301</v>
+        <v>-22.36391624832774</v>
       </c>
       <c r="F62">
-        <v>-3.730455826768954</v>
+        <v>-4.433564966223743</v>
       </c>
       <c r="G62">
-        <v>-9.761301629387441</v>
+        <v>-12.66818174600135</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.439846128387368</v>
       </c>
       <c r="E63">
-        <v>-17.44704861044152</v>
+        <v>-22.61797269710606</v>
       </c>
       <c r="F63">
-        <v>-3.664007507185989</v>
+        <v>-4.067105167634075</v>
       </c>
       <c r="G63">
-        <v>-10.10987892053349</v>
+        <v>-12.15970068459888</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.604505402440701</v>
       </c>
       <c r="E64">
-        <v>-18.54138152523911</v>
+        <v>-23.47105568761902</v>
       </c>
       <c r="F64">
-        <v>-3.808564245913725</v>
+        <v>-4.414403999829588</v>
       </c>
       <c r="G64">
-        <v>-9.803603137731802</v>
+        <v>-11.99287025563047</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.748361148035656</v>
       </c>
       <c r="E65">
-        <v>-17.46724107604172</v>
+        <v>-22.0970351611597</v>
       </c>
       <c r="F65">
-        <v>-3.948342961462113</v>
+        <v>-4.436186749053603</v>
       </c>
       <c r="G65">
-        <v>-9.754532469310307</v>
+        <v>-12.97330253881411</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.869916301158112</v>
       </c>
       <c r="E66">
-        <v>-17.62679280075397</v>
+        <v>-22.41995611417266</v>
       </c>
       <c r="F66">
-        <v>-4.029369718966947</v>
+        <v>-4.334019227061924</v>
       </c>
       <c r="G66">
-        <v>-10.11329139095531</v>
+        <v>-12.0961302981062</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.975962877240462</v>
       </c>
       <c r="E67">
-        <v>-17.99445507696272</v>
+        <v>-22.92343638281946</v>
       </c>
       <c r="F67">
-        <v>-3.787744887979165</v>
+        <v>-3.98153564329229</v>
       </c>
       <c r="G67">
-        <v>-10.55684035891793</v>
+        <v>-13.28242314070784</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.06951866367811</v>
       </c>
       <c r="E68">
-        <v>-17.3366353571865</v>
+        <v>-22.50702055544413</v>
       </c>
       <c r="F68">
-        <v>-4.113259314215855</v>
+        <v>-4.44736473878698</v>
       </c>
       <c r="G68">
-        <v>-10.29917587351942</v>
+        <v>-12.73403258147784</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.15923325627962</v>
       </c>
       <c r="E69">
-        <v>-17.88080396479221</v>
+        <v>-22.17851599397971</v>
       </c>
       <c r="F69">
-        <v>-3.961494122348958</v>
+        <v>-4.170766236053003</v>
       </c>
       <c r="G69">
-        <v>-10.04642337679539</v>
+        <v>-12.26233073253519</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.2480016317533</v>
       </c>
       <c r="E70">
-        <v>-16.56875107665385</v>
+        <v>-21.6276814726347</v>
       </c>
       <c r="F70">
-        <v>-3.686683236470222</v>
+        <v>-4.457625725805458</v>
       </c>
       <c r="G70">
-        <v>-10.18399187189667</v>
+        <v>-12.27179377551263</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.33836140137742</v>
       </c>
       <c r="E71">
-        <v>-17.31120797563343</v>
+        <v>-22.39979987636452</v>
       </c>
       <c r="F71">
-        <v>-4.226502108382965</v>
+        <v>-4.441246417149904</v>
       </c>
       <c r="G71">
-        <v>-9.638941596214188</v>
+        <v>-12.48839049187313</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.42856029514953</v>
       </c>
       <c r="E72">
-        <v>-16.3127292701562</v>
+        <v>-22.06531320073596</v>
       </c>
       <c r="F72">
-        <v>-4.17985839666613</v>
+        <v>-4.345497914162516</v>
       </c>
       <c r="G72">
-        <v>-10.4247613474856</v>
+        <v>-13.13738986655882</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.51554489684382</v>
       </c>
       <c r="E73">
-        <v>-17.45109706620438</v>
+        <v>-22.21980661998165</v>
       </c>
       <c r="F73">
-        <v>-3.903920102752184</v>
+        <v>-4.572820981940965</v>
       </c>
       <c r="G73">
-        <v>-9.616921318328755</v>
+        <v>-11.87562564686839</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.59643178833342</v>
       </c>
       <c r="E74">
-        <v>-17.37663989657026</v>
+        <v>-22.48621674585289</v>
       </c>
       <c r="F74">
-        <v>-4.230103021482934</v>
+        <v>-4.813584310829836</v>
       </c>
       <c r="G74">
-        <v>-9.388325174725361</v>
+        <v>-13.06895670971504</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.66693395376718</v>
       </c>
       <c r="E75">
-        <v>-16.87723978300437</v>
+        <v>-22.81540963536648</v>
       </c>
       <c r="F75">
-        <v>-4.313720912223725</v>
+        <v>-4.567261808300778</v>
       </c>
       <c r="G75">
-        <v>-9.674595349679114</v>
+        <v>-11.76180991463593</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.72562796357014</v>
       </c>
       <c r="E76">
-        <v>-17.41771315581983</v>
+        <v>-23.37640152391069</v>
       </c>
       <c r="F76">
-        <v>-4.290538222088978</v>
+        <v>-4.435347612874568</v>
       </c>
       <c r="G76">
-        <v>-9.428083736361152</v>
+        <v>-12.05135474870601</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.76621023862641</v>
       </c>
       <c r="E77">
-        <v>-17.63804153018902</v>
+        <v>-22.19786163494047</v>
       </c>
       <c r="F77">
-        <v>-4.193243157160564</v>
+        <v>-4.73706635709844</v>
       </c>
       <c r="G77">
-        <v>-8.939942967405681</v>
+        <v>-11.43432759689555</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.7877668029687</v>
       </c>
       <c r="E78">
-        <v>-18.72802710993925</v>
+        <v>-23.37507920950045</v>
       </c>
       <c r="F78">
-        <v>-4.471414729592459</v>
+        <v>-5.255500924507913</v>
       </c>
       <c r="G78">
-        <v>-9.685511973807387</v>
+        <v>-10.84409161911796</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.78356636389963</v>
       </c>
       <c r="E79">
-        <v>-18.85825696545183</v>
+        <v>-23.24372176395996</v>
       </c>
       <c r="F79">
-        <v>-4.367877087916548</v>
+        <v>-5.048269079716964</v>
       </c>
       <c r="G79">
-        <v>-9.398004778325722</v>
+        <v>-10.25175237832076</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.75607788142503</v>
       </c>
       <c r="E80">
-        <v>-19.04393345671433</v>
+        <v>-25.35366007293178</v>
       </c>
       <c r="F80">
-        <v>-4.714360806587706</v>
+        <v>-5.207613004952075</v>
       </c>
       <c r="G80">
-        <v>-8.95566001867542</v>
+        <v>-11.54427476890943</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.70242026325795</v>
       </c>
       <c r="E81">
-        <v>-19.86781231835182</v>
+        <v>-25.2354714298056</v>
       </c>
       <c r="F81">
-        <v>-4.716218006304782</v>
+        <v>-4.72188072587032</v>
       </c>
       <c r="G81">
-        <v>-8.925249657262487</v>
+        <v>-11.38139493069859</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.6305040509148</v>
       </c>
       <c r="E82">
-        <v>-20.09202159494559</v>
+        <v>-25.7172286086376</v>
       </c>
       <c r="F82">
-        <v>-4.809574184232884</v>
+        <v>-6.001647892375152</v>
       </c>
       <c r="G82">
-        <v>-8.21490784552298</v>
+        <v>-10.30925906737159</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.54058875435602</v>
       </c>
       <c r="E83">
-        <v>-20.4218167715022</v>
+        <v>-25.84257676916992</v>
       </c>
       <c r="F83">
-        <v>-4.921273729928577</v>
+        <v>-5.365950463792783</v>
       </c>
       <c r="G83">
-        <v>-9.018305100688339</v>
+        <v>-11.8935378353614</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.44215839993118</v>
       </c>
       <c r="E84">
-        <v>-20.85002927366751</v>
+        <v>-26.05479464659137</v>
       </c>
       <c r="F84">
-        <v>-4.9586521522451</v>
+        <v>-5.352730548411506</v>
       </c>
       <c r="G84">
-        <v>-8.273224996298991</v>
+        <v>-10.92415014394685</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.33535698610237</v>
       </c>
       <c r="E85">
-        <v>-22.36464533264297</v>
+        <v>-28.12048070756024</v>
       </c>
       <c r="F85">
-        <v>-4.989392866562989</v>
+        <v>-5.412620683266507</v>
       </c>
       <c r="G85">
-        <v>-8.596385945245581</v>
+        <v>-11.42334206711453</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.2302443530248</v>
       </c>
       <c r="E86">
-        <v>-23.6414304652096</v>
+        <v>-28.06607109235808</v>
       </c>
       <c r="F86">
-        <v>-5.310798590481794</v>
+        <v>-5.702589864249071</v>
       </c>
       <c r="G86">
-        <v>-8.58936413110837</v>
+        <v>-10.15362416636401</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.1283977548644</v>
       </c>
       <c r="E87">
-        <v>-24.5610140965252</v>
+        <v>-29.08216103325114</v>
       </c>
       <c r="F87">
-        <v>-5.434191370435406</v>
+        <v>-6.048077885302064</v>
       </c>
       <c r="G87">
-        <v>-8.831728280375193</v>
+        <v>-10.15075965994261</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.0403976304668</v>
       </c>
       <c r="E88">
-        <v>-26.0920051175124</v>
+        <v>-29.81287107065483</v>
       </c>
       <c r="F88">
-        <v>-5.325131831652435</v>
+        <v>-6.070233399857339</v>
       </c>
       <c r="G88">
-        <v>-8.746058866679652</v>
+        <v>-10.73400335457703</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.96895727768916</v>
       </c>
       <c r="E89">
-        <v>-27.54265648112952</v>
+        <v>-31.02685758992008</v>
       </c>
       <c r="F89">
-        <v>-5.519383159241515</v>
+        <v>-5.649870906000105</v>
       </c>
       <c r="G89">
-        <v>-8.799746213835286</v>
+        <v>-11.11188523547048</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.923593134249435</v>
       </c>
       <c r="E90">
-        <v>-28.37072418122411</v>
+        <v>-34.10295035690239</v>
       </c>
       <c r="F90">
-        <v>-5.351344689746622</v>
+        <v>-6.164828815420029</v>
       </c>
       <c r="G90">
-        <v>-8.869377016548263</v>
+        <v>-10.69219074824503</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.908036341512384</v>
       </c>
       <c r="E91">
-        <v>-30.61394680142669</v>
+        <v>-34.77223164439202</v>
       </c>
       <c r="F91">
-        <v>-5.558183060021242</v>
+        <v>-6.294443877119769</v>
       </c>
       <c r="G91">
-        <v>-9.128626331959989</v>
+        <v>-10.95508878203086</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.929180687667381</v>
       </c>
       <c r="E92">
-        <v>-32.05669371366343</v>
+        <v>-36.63729724987308</v>
       </c>
       <c r="F92">
-        <v>-5.6865311337784</v>
+        <v>-6.15327143341617</v>
       </c>
       <c r="G92">
-        <v>-9.832087422089343</v>
+        <v>-11.42081552651376</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.992092253930673</v>
       </c>
       <c r="E93">
-        <v>-34.39216587787627</v>
+        <v>-37.32684345854704</v>
       </c>
       <c r="F93">
-        <v>-5.63304179384483</v>
+        <v>-6.104810283617594</v>
       </c>
       <c r="G93">
-        <v>-9.867668988679961</v>
+        <v>-11.98661296611661</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.09872675805881</v>
       </c>
       <c r="E94">
-        <v>-34.70748805150436</v>
+        <v>-38.25365906285288</v>
       </c>
       <c r="F94">
-        <v>-5.45524846981457</v>
+        <v>-5.762322609297541</v>
       </c>
       <c r="G94">
-        <v>-9.681791068558978</v>
+        <v>-12.43687531338985</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.25271255198835</v>
       </c>
       <c r="E95">
-        <v>-38.0117887376292</v>
+        <v>-41.50763708156749</v>
       </c>
       <c r="F95">
-        <v>-5.527636183675607</v>
+        <v>-6.368187214235488</v>
       </c>
       <c r="G95">
-        <v>-11.07392478324926</v>
+        <v>-12.07972747153053</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.45574152603592</v>
       </c>
       <c r="E96">
-        <v>-39.32793763050751</v>
+        <v>-44.03536334553897</v>
       </c>
       <c r="F96">
-        <v>-5.234368443695096</v>
+        <v>-6.868183565809749</v>
       </c>
       <c r="G96">
-        <v>-11.22057898084865</v>
+        <v>-12.70753999860689</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.70643251350046</v>
       </c>
       <c r="E97">
-        <v>-42.00552921328882</v>
+        <v>-45.27007216186333</v>
       </c>
       <c r="F97">
-        <v>-5.430894468172264</v>
+        <v>-6.191937967044045</v>
       </c>
       <c r="G97">
-        <v>-10.78626665157586</v>
+        <v>-13.19409265632759</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.01008957258141</v>
       </c>
       <c r="E98">
-        <v>-43.84199524117444</v>
+        <v>-47.60244911409193</v>
       </c>
       <c r="F98">
-        <v>-5.663647484276064</v>
+        <v>-6.054939252499452</v>
       </c>
       <c r="G98">
-        <v>-11.4750606813345</v>
+        <v>-13.3269985355929</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.35435573588516</v>
       </c>
       <c r="E99">
-        <v>-46.32504358058625</v>
+        <v>-50.88544785848469</v>
       </c>
       <c r="F99">
-        <v>-5.240176955923525</v>
+        <v>-6.370498359289298</v>
       </c>
       <c r="G99">
-        <v>-11.46592904173457</v>
+        <v>-14.02048307157076</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.75769713845419</v>
       </c>
       <c r="E100">
-        <v>-48.17471011020422</v>
+        <v>-52.07481872516275</v>
       </c>
       <c r="F100">
-        <v>-5.101282108393924</v>
+        <v>-5.748406036930509</v>
       </c>
       <c r="G100">
-        <v>-12.07512063646107</v>
+        <v>-13.50106405809988</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.18038156878088</v>
       </c>
       <c r="E101">
-        <v>-50.80692864766569</v>
+        <v>-54.73156234573126</v>
       </c>
       <c r="F101">
-        <v>-5.069669951568289</v>
+        <v>-5.805871540397517</v>
       </c>
       <c r="G101">
-        <v>-12.88732469029198</v>
+        <v>-14.57910776084466</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.67959592365814</v>
       </c>
       <c r="E102">
-        <v>-53.20114078035052</v>
+        <v>-55.66398986145111</v>
       </c>
       <c r="F102">
-        <v>-5.166174753994432</v>
+        <v>-6.418133626787284</v>
       </c>
       <c r="G102">
-        <v>-12.8878004674181</v>
+        <v>-16.1660623650162</v>
       </c>
     </row>
   </sheetData>
